--- a/jogos_2025-10-25.xlsx
+++ b/jogos_2025-10-25.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4068,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N94" t="n">
-        <v>3.37</v>
+        <v>4.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="N101" t="n">
-        <v>2.75</v>
+        <v>1.28</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>9</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="N105" t="n">
-        <v>1.28</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,16 +13995,16 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N106" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z106" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z106" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AA106" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,22 +18951,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA155" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,22 +21402,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,22 +21660,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21789,22 +21789,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,22 +22047,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22380,10 +22380,10 @@
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z170" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,22 +22821,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,22 +23079,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26598,13 +26598,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26643,10 +26643,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27675,10 +27675,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,10 +27798,10 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z212" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M222" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N222" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29787,22 +29787,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,10 +32571,10 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
         <v>0</v>
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="M254" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N254" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,7 +33216,7 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Z254" t="n">
         <v>1.97</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Moghayer Al Sarhan</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,16 +33732,16 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Moghayer Al Sarhan</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z260" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="M262" t="n">
-        <v>4.9</v>
+        <v>3.84</v>
       </c>
       <c r="N262" t="n">
-        <v>7</v>
+        <v>3.36</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,16 +34248,16 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z262" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AA262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34512,10 +34512,10 @@
         <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB264" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M268" t="n">
         <v>3.95</v>
       </c>
       <c r="N268" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,7 +35022,7 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z268" t="n">
         <v>2.35</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35151,10 +35151,10 @@
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z269" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA269" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z270" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z272" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35628,13 +35628,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M273" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N273" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -35667,10 +35667,10 @@
         <v>0</v>
       </c>
       <c r="Y273" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z273" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA273" t="n">
         <v>0</v>
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36660,13 +36660,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -36699,10 +36699,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z281" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="M283" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N283" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,10 +36957,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -37011,22 +37011,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37140,22 +37140,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>3.11</v>
+        <v>1.72</v>
       </c>
       <c r="M285" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N285" t="n">
-        <v>2.27</v>
+        <v>4.6</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="M290" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N290" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z290" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="M291" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N291" t="n">
-        <v>3.95</v>
+        <v>1.6</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Z291" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,22 +38430,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,16 +38505,16 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z295" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA295" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38595,13 +38595,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -38634,16 +38634,16 @@
         <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z296" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB296" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M299" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N299" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -39027,10 +39027,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB299" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39627,13 +39627,13 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="M304" t="n">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
       <c r="N304" t="n">
-        <v>2.8</v>
+        <v>15</v>
       </c>
       <c r="O304" t="n">
         <v>0</v>
@@ -39666,16 +39666,16 @@
         <v>0</v>
       </c>
       <c r="Y304" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z304" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="AA304" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB304" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC304" t="n">
         <v>0</v>
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39756,13 +39756,13 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="M305" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="N305" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="O305" t="n">
         <v>0</v>
@@ -39795,16 +39795,16 @@
         <v>0</v>
       </c>
       <c r="Y305" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="Z305" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA305" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB305" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC305" t="n">
         <v>0</v>
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41562,13 +41562,13 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N319" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41820,13 +41820,13 @@
         </is>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M321" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -42042,22 +42042,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42078,13 +42078,13 @@
         </is>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M323" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O323" t="n">
         <v>0</v>
@@ -42117,10 +42117,10 @@
         <v>0</v>
       </c>
       <c r="Y323" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z323" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA323" t="n">
         <v>0</v>
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42429,22 +42429,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42465,13 +42465,13 @@
         </is>
       </c>
       <c r="L326" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N326" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O326" t="n">
         <v>0</v>
@@ -42504,10 +42504,10 @@
         <v>0</v>
       </c>
       <c r="Y326" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z326" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA326" t="n">
         <v>0</v>

--- a/jogos_2025-10-25.xlsx
+++ b/jogos_2025-10-25.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
         <v>3.7</v>
@@ -714,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4068,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="M84" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N84" t="n">
-        <v>3.37</v>
+        <v>5.55</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="M94" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="N94" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>1.65</v>
       </c>
       <c r="M101" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="N101" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13743,10 +13743,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="M108" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N108" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,22 +21660,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,22 +21789,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,22 +21918,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,22 +22047,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA172" t="n">
         <v>0</v>
@@ -22692,22 +22692,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,22 +22950,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z191" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27675,10 +27675,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,10 +27798,10 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28707,10 +28707,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M221" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N221" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z246" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M258" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="N258" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,16 +33732,16 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z258" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Moghayer Al Sarhan</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z262" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Moghayer Al Sarhan</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L263" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M264" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N264" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,16 +34506,16 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z264" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA264" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB264" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,10 +34635,10 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z265" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35151,10 +35151,10 @@
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA269" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="M270" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N270" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z270" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z272" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35628,13 +35628,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -35667,10 +35667,10 @@
         <v>0</v>
       </c>
       <c r="Y273" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z273" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA273" t="n">
         <v>0</v>
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>9.300000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="M282" t="n">
-        <v>4.95</v>
+        <v>3.3</v>
       </c>
       <c r="N282" t="n">
-        <v>1.32</v>
+        <v>4.6</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.35</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M283" t="n">
-        <v>3.85</v>
+        <v>4.95</v>
       </c>
       <c r="N283" t="n">
-        <v>2.75</v>
+        <v>1.32</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,10 +36957,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z283" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -37011,22 +37011,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37140,22 +37140,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.72</v>
+        <v>3.11</v>
       </c>
       <c r="M285" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N285" t="n">
-        <v>4.6</v>
+        <v>2.27</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="M290" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N290" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z290" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z291" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,22 +38043,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38079,13 +38079,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -38118,10 +38118,10 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z292" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA292" t="n">
         <v>0</v>
@@ -38172,7 +38172,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -38182,12 +38182,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -38247,16 +38247,16 @@
         <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z293" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA293" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,16 +38505,16 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z295" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -38569,12 +38569,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38898,10 +38898,10 @@
         <v>0</v>
       </c>
       <c r="AA298" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB298" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC298" t="n">
         <v>0</v>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N299" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -39027,10 +39027,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB299" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -39075,7 +39075,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40788,13 +40788,13 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N313" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -40827,10 +40827,10 @@
         <v>0</v>
       </c>
       <c r="Y313" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z313" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA313" t="n">
         <v>0</v>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -42042,22 +42042,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42078,13 +42078,13 @@
         </is>
       </c>
       <c r="L323" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N323" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O323" t="n">
         <v>0</v>
@@ -42117,10 +42117,10 @@
         <v>0</v>
       </c>
       <c r="Y323" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z323" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA323" t="n">
         <v>0</v>
@@ -42300,22 +42300,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42336,13 +42336,13 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M325" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N325" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O325" t="n">
         <v>0</v>
@@ -42375,10 +42375,10 @@
         <v>0</v>
       </c>
       <c r="Y325" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z325" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA325" t="n">
         <v>0</v>
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G326" t="n">

--- a/jogos_2025-10-25.xlsx
+++ b/jogos_2025-10-25.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45955.38541666666</v>
+        <v>45955.375</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45955.39583333334</v>
+        <v>45955.375</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45955.39583333334</v>
+        <v>45955.375</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45955.39583333334</v>
+        <v>45955.38541666666</v>
       </c>
     </row>
     <row r="62">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45955.40625</v>
+        <v>45955.39583333334</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45955.41666666666</v>
+        <v>45955.39583333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45955.41666666666</v>
+        <v>45955.39583333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45955.41666666666</v>
+        <v>45955.40625</v>
       </c>
     </row>
     <row r="79">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.75</v>
+        <v>1.22</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="N79" t="n">
-        <v>2.7</v>
+        <v>18</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M87" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>3.37</v>
+        <v>2.55</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.65</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="N101" t="n">
-        <v>4.8</v>
+        <v>1.28</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13743,10 +13743,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M104" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="M105" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="N105" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14001,10 +14001,10 @@
         <v>2.3</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N132" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19671,10 +19671,10 @@
         <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,22 +21918,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z172" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA172" t="n">
         <v>0</v>
@@ -22692,22 +22692,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,22 +23079,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z189" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,10 +27798,10 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z212" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z214" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28578,10 +28578,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28707,10 +28707,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31668,10 +31668,10 @@
         <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA242" t="n">
         <v>0</v>
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,10 +33345,10 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z255" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA255" t="n">
         <v>0</v>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33738,10 +33738,10 @@
         <v>0</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
         <v>0</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Moghayer Al Sarhan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34334,17 +34334,17 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="M264" t="n">
-        <v>4.9</v>
+        <v>3.84</v>
       </c>
       <c r="N264" t="n">
-        <v>7</v>
+        <v>3.36</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,16 +34506,16 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="Z264" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AA264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="M265" t="n">
-        <v>3.84</v>
+        <v>4.9</v>
       </c>
       <c r="N265" t="n">
-        <v>3.36</v>
+        <v>7</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,16 +34635,16 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="Z265" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AA265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB265" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34704,7 +34704,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Moghayer Al Sarhan</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34721,7 +34721,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z267" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N270" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z270" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="M272" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N272" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z272" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35757,13 +35757,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -35796,10 +35796,10 @@
         <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z274" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA274" t="n">
         <v>0</v>
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.72</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M282" t="n">
-        <v>3.3</v>
+        <v>4.95</v>
       </c>
       <c r="N282" t="n">
-        <v>4.6</v>
+        <v>1.32</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>9.300000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="M283" t="n">
-        <v>4.95</v>
+        <v>3.85</v>
       </c>
       <c r="N283" t="n">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,10 +36957,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z283" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -37011,22 +37011,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37140,22 +37140,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>3.11</v>
+        <v>1.72</v>
       </c>
       <c r="M285" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N285" t="n">
-        <v>2.27</v>
+        <v>4.6</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z290" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z291" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38079,13 +38079,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="M292" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N292" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -38118,10 +38118,10 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z292" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AA292" t="n">
         <v>0</v>
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N293" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -38247,16 +38247,16 @@
         <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z293" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,7 +38688,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -38698,12 +38698,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38724,13 +38724,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -38769,10 +38769,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M298" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N298" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38886,22 +38886,22 @@
         <v>0</v>
       </c>
       <c r="W298" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X298" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y298" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z298" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA298" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB298" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC298" t="n">
         <v>0</v>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M299" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -39021,16 +39021,16 @@
         <v>0</v>
       </c>
       <c r="Y299" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z299" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA299" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB299" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -39075,22 +39075,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39111,13 +39111,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M300" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -39150,10 +39150,10 @@
         <v>0</v>
       </c>
       <c r="Y300" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z300" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA300" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,22 +39333,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39627,13 +39627,13 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="M304" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="N304" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="O304" t="n">
         <v>0</v>
@@ -39666,16 +39666,16 @@
         <v>0</v>
       </c>
       <c r="Y304" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="Z304" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA304" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB304" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC304" t="n">
         <v>0</v>
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39756,13 +39756,13 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>2.6</v>
+        <v>1.16</v>
       </c>
       <c r="M305" t="n">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
       <c r="N305" t="n">
-        <v>2.8</v>
+        <v>15</v>
       </c>
       <c r="O305" t="n">
         <v>0</v>
@@ -39795,16 +39795,16 @@
         <v>0</v>
       </c>
       <c r="Y305" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z305" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="AA305" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB305" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC305" t="n">
         <v>0</v>
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40530,13 +40530,13 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M311" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N311" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -40569,10 +40569,10 @@
         <v>0</v>
       </c>
       <c r="Y311" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z311" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA311" t="n">
         <v>0</v>
@@ -40659,13 +40659,13 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M312" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N312" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O312" t="n">
         <v>0</v>
@@ -40698,10 +40698,10 @@
         <v>0</v>
       </c>
       <c r="Y312" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z312" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA312" t="n">
         <v>0</v>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40788,13 +40788,13 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M313" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N313" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -40827,10 +40827,10 @@
         <v>0</v>
       </c>
       <c r="Y313" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z313" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA313" t="n">
         <v>0</v>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N314" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z314" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41691,13 +41691,13 @@
         </is>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M320" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O320" t="n">
         <v>0</v>
@@ -41730,10 +41730,10 @@
         <v>0</v>
       </c>
       <c r="Y320" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z320" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA320" t="n">
         <v>0</v>
@@ -41859,10 +41859,10 @@
         <v>0</v>
       </c>
       <c r="Y321" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z321" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA321" t="n">
         <v>0</v>
@@ -41913,22 +41913,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -41949,13 +41949,13 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M322" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N322" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
@@ -41988,10 +41988,10 @@
         <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z322" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA322" t="n">
         <v>0</v>
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42300,22 +42300,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42336,13 +42336,13 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N325" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O325" t="n">
         <v>0</v>
@@ -42375,10 +42375,10 @@
         <v>0</v>
       </c>
       <c r="Y325" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z325" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA325" t="n">
         <v>0</v>
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G326" t="n">

--- a/jogos_2025-10-25.xlsx
+++ b/jogos_2025-10-25.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.22</v>
+        <v>3.5</v>
       </c>
       <c r="M79" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="N79" t="n">
-        <v>18</v>
+        <v>2.05</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z79" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="M89" t="n">
         <v>3.55</v>
       </c>
       <c r="N89" t="n">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13485,10 +13485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13614,10 +13614,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="N105" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14001,10 +14001,10 @@
         <v>2.3</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N125" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="M132" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N132" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="M140" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N140" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="M142" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N142" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M148" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N148" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z148" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="M149" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N149" t="n">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19671,10 +19671,10 @@
         <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z149" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AA149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -19800,10 +19800,10 @@
         <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19890,13 +19890,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -19929,10 +19929,10 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20439,10 +20439,10 @@
         <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y155" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22305,22 +22305,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28578,10 +28578,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28791,13 +28791,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -28836,10 +28836,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,10 +33345,10 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
         <v>0</v>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z256" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Moghayer Al Sarhan</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,16 +34635,16 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z265" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB265" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Moghayer Al Sarhan</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34721,17 +34721,17 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,16 +34764,16 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z266" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB266" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="M269" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="N269" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35145,16 +35145,16 @@
         <v>0</v>
       </c>
       <c r="W269" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X269" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y269" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z269" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA269" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z270" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z272" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36660,13 +36660,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -36699,10 +36699,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z281" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -36753,22 +36753,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>9.300000000000001</v>
+        <v>3.11</v>
       </c>
       <c r="M282" t="n">
-        <v>4.95</v>
+        <v>3.25</v>
       </c>
       <c r="N282" t="n">
-        <v>1.32</v>
+        <v>2.27</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.35</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M283" t="n">
-        <v>3.85</v>
+        <v>4.95</v>
       </c>
       <c r="N283" t="n">
-        <v>2.75</v>
+        <v>1.32</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,10 +36957,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z283" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -37011,22 +37011,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="M291" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N291" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z291" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38079,13 +38079,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="M292" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="N292" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -38118,10 +38118,10 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z292" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AA292" t="n">
         <v>0</v>
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38337,13 +38337,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -38382,10 +38382,10 @@
         <v>0</v>
       </c>
       <c r="AA294" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC294" t="n">
         <v>0</v>
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,16 +38505,16 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z295" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA295" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38595,13 +38595,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -38634,10 +38634,10 @@
         <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z296" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA296" t="n">
         <v>0</v>
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38724,13 +38724,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -38769,10 +38769,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N298" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38886,16 +38886,16 @@
         <v>0</v>
       </c>
       <c r="W298" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X298" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y298" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z298" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA298" t="n">
         <v>0</v>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N299" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -39021,16 +39021,16 @@
         <v>0</v>
       </c>
       <c r="Y299" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z299" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB299" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39111,13 +39111,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M300" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N300" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -39144,16 +39144,16 @@
         <v>0</v>
       </c>
       <c r="W300" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X300" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y300" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z300" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA300" t="n">
         <v>0</v>
@@ -39333,7 +39333,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40401,13 +40401,13 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M310" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -40440,10 +40440,10 @@
         <v>0</v>
       </c>
       <c r="Y310" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z310" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA310" t="n">
         <v>0</v>
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40530,13 +40530,13 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N311" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -40569,10 +40569,10 @@
         <v>0</v>
       </c>
       <c r="Y311" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z311" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA311" t="n">
         <v>0</v>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40788,13 +40788,13 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N313" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -40827,10 +40827,10 @@
         <v>0</v>
       </c>
       <c r="Y313" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z313" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA313" t="n">
         <v>0</v>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41268,7 +41268,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G326" t="n">
